--- a/raw_data/OSL_Demonstration_Data_Collection_in_Tea_Plantation.xlsx
+++ b/raw_data/OSL_Demonstration_Data_Collection_in_Tea_Plantation.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Benjamin\Documents\Bukombe_manuscripts\OA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Benjamin\Oath Dropbox\Benjamin Bukombe\tea_paper\raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{066E5273-B54D-48F2-AFED-7D08AB75A62A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F0B2143-57C2-4626-A1CF-67078FF5F20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -36,12 +36,6 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="19">
   <si>
     <t>Timestamp</t>
-  </si>
-  <si>
-    <t>Farm</t>
-  </si>
-  <si>
-    <t>treatment</t>
   </si>
   <si>
     <t>data_entry</t>
@@ -90,6 +84,12 @@
   </si>
   <si>
     <t>yield_kg</t>
+  </si>
+  <si>
+    <t>Site</t>
+  </si>
+  <si>
+    <t>Treatment</t>
   </si>
 </sst>
 </file>
@@ -218,8 +218,8 @@
   <tableColumns count="8">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Timestamp"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="date"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Farm"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="treatment"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Site"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Treatment"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="area_ha"/>
     <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="yield_kg"/>
     <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="data_entry"/>
@@ -443,25 +443,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -472,10 +472,10 @@
         <v>46006</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E2" s="4">
         <v>3</v>
@@ -484,7 +484,7 @@
         <v>496</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" s="4"/>
     </row>
@@ -496,10 +496,10 @@
         <v>46006</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E3" s="4">
         <v>1.5</v>
@@ -508,7 +508,7 @@
         <v>198</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H3" s="4"/>
     </row>
@@ -520,10 +520,10 @@
         <v>46009</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E4" s="4">
         <v>2.5000000000000001E-3</v>
@@ -532,7 +532,7 @@
         <v>1.02</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H4" s="4">
         <v>1</v>
@@ -546,10 +546,10 @@
         <v>46009</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E5" s="4">
         <v>2.5000000000000001E-3</v>
@@ -558,7 +558,7 @@
         <v>0.87</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H5" s="4">
         <v>1</v>
@@ -572,10 +572,10 @@
         <v>46009</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E6" s="4">
         <v>2.5000000000000001E-3</v>
@@ -584,7 +584,7 @@
         <v>0.8</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H6" s="4">
         <v>1</v>
@@ -598,10 +598,10 @@
         <v>46009</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E7" s="4">
         <v>2.5000000000000001E-3</v>
@@ -610,7 +610,7 @@
         <v>0.93</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H7" s="4">
         <v>1</v>
@@ -624,10 +624,10 @@
         <v>46009</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E8" s="4">
         <v>2.5000000000000001E-3</v>
@@ -636,7 +636,7 @@
         <v>1.03</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H8" s="4">
         <v>1</v>
@@ -650,10 +650,10 @@
         <v>46009</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E9" s="4">
         <v>2.5000000000000001E-3</v>
@@ -662,7 +662,7 @@
         <v>1.5</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H9" s="4">
         <v>2</v>
@@ -676,10 +676,10 @@
         <v>46009</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E10" s="4">
         <v>2.5000000000000001E-3</v>
@@ -688,7 +688,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H10" s="4">
         <v>2</v>
@@ -702,10 +702,10 @@
         <v>46009</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E11" s="4">
         <v>2.5000000000000001E-3</v>
@@ -714,7 +714,7 @@
         <v>1.1399999999999999</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H11" s="4">
         <v>2</v>
@@ -728,10 +728,10 @@
         <v>46009</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E12" s="4">
         <v>2.5000000000000001E-3</v>
@@ -740,7 +740,7 @@
         <v>1.41</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H12" s="4">
         <v>2</v>
@@ -754,10 +754,10 @@
         <v>46009</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E13" s="4">
         <v>2.5000000000000001E-3</v>
@@ -766,7 +766,7 @@
         <v>0.68</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H13" s="4">
         <v>2</v>
@@ -780,10 +780,10 @@
         <v>46009</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E14" s="4">
         <v>2.5000000000000001E-3</v>
@@ -792,7 +792,7 @@
         <v>0.69</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H14" s="4">
         <v>3</v>
@@ -806,10 +806,10 @@
         <v>46009</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E15" s="4">
         <v>2.5000000000000001E-3</v>
@@ -818,7 +818,7 @@
         <v>0.87</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H15" s="4">
         <v>3</v>
@@ -832,10 +832,10 @@
         <v>46009</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E16" s="4">
         <v>2.5000000000000001E-3</v>
@@ -844,7 +844,7 @@
         <v>1.24</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H16" s="4">
         <v>3</v>
@@ -858,10 +858,10 @@
         <v>46009</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E17" s="4">
         <v>2.5000000000000001E-3</v>
@@ -870,7 +870,7 @@
         <v>1.3</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H17" s="4">
         <v>3</v>
@@ -884,10 +884,10 @@
         <v>46009</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E18" s="4">
         <v>2.5000000000000001E-3</v>
@@ -896,7 +896,7 @@
         <v>0.31</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H18" s="4">
         <v>3</v>
@@ -910,10 +910,10 @@
         <v>46009</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E19" s="4">
         <v>2.5000000000000001E-3</v>
@@ -922,7 +922,7 @@
         <v>0.85</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H19" s="4">
         <v>4</v>
@@ -936,10 +936,10 @@
         <v>46009</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E20" s="4">
         <v>2.5000000000000001E-3</v>
@@ -948,7 +948,7 @@
         <v>0.63</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H20" s="4">
         <v>4</v>
@@ -962,10 +962,10 @@
         <v>46009</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E21" s="4">
         <v>2.5000000000000001E-3</v>
@@ -974,7 +974,7 @@
         <v>0.81</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H21" s="4">
         <v>4</v>
@@ -988,10 +988,10 @@
         <v>46009</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E22" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1000,7 +1000,7 @@
         <v>0.7</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H22" s="4">
         <v>4</v>
@@ -1014,10 +1014,10 @@
         <v>46009</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E23" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1026,7 +1026,7 @@
         <v>0.25</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H23" s="4">
         <v>4</v>
@@ -1040,10 +1040,10 @@
         <v>46014</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E24" s="4">
         <v>0.2</v>
@@ -1052,7 +1052,7 @@
         <v>138</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1063,10 +1063,10 @@
         <v>46014</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E25" s="4">
         <v>0.2</v>
@@ -1075,7 +1075,7 @@
         <v>64.900000000000006</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1086,10 +1086,10 @@
         <v>46020</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E26" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1098,7 +1098,7 @@
         <v>3.03</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H26" s="4">
         <v>1</v>
@@ -1112,10 +1112,10 @@
         <v>46020</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E27" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1124,7 +1124,7 @@
         <v>3.03</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H27" s="4">
         <v>1</v>
@@ -1138,10 +1138,10 @@
         <v>46020</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E28" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1150,7 +1150,7 @@
         <v>2.5099999999999998</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H28" s="4">
         <v>1</v>
@@ -1164,10 +1164,10 @@
         <v>46020</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E29" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1176,7 +1176,7 @@
         <v>2.15</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H29" s="4">
         <v>1</v>
@@ -1190,10 +1190,10 @@
         <v>46020</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E30" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1202,7 +1202,7 @@
         <v>1.7</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H30" s="4">
         <v>1</v>
@@ -1216,10 +1216,10 @@
         <v>46020</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E31" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1228,7 +1228,7 @@
         <v>2.72</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H31" s="4">
         <v>2</v>
@@ -1242,10 +1242,10 @@
         <v>46020</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E32" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1254,7 +1254,7 @@
         <v>2.4</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H32" s="4">
         <v>2</v>
@@ -1268,10 +1268,10 @@
         <v>46020</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E33" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1280,7 +1280,7 @@
         <v>2.56</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H33" s="4">
         <v>2</v>
@@ -1294,10 +1294,10 @@
         <v>46020</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E34" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1306,7 +1306,7 @@
         <v>3.11</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H34" s="4">
         <v>2</v>
@@ -1320,10 +1320,10 @@
         <v>46020</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E35" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1332,7 +1332,7 @@
         <v>1.77</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H35" s="4">
         <v>2</v>
@@ -1346,10 +1346,10 @@
         <v>46020</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E36" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1358,7 +1358,7 @@
         <v>2.02</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H36" s="4">
         <v>3</v>
@@ -1372,10 +1372,10 @@
         <v>46020</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E37" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1384,7 +1384,7 @@
         <v>2.0499999999999998</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H37" s="4">
         <v>3</v>
@@ -1398,10 +1398,10 @@
         <v>46020</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E38" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1410,7 +1410,7 @@
         <v>2.94</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H38" s="4">
         <v>3</v>
@@ -1424,10 +1424,10 @@
         <v>46020</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E39" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1436,7 +1436,7 @@
         <v>2.2000000000000002</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H39" s="4">
         <v>3</v>
@@ -1450,10 +1450,10 @@
         <v>46020</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E40" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1462,7 +1462,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H40" s="4">
         <v>3</v>
@@ -1476,10 +1476,10 @@
         <v>46020</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E41" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1488,7 +1488,7 @@
         <v>1.61</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H41" s="4">
         <v>4</v>
@@ -1502,10 +1502,10 @@
         <v>46020</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E42" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1514,7 +1514,7 @@
         <v>1.26</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H42" s="4">
         <v>4</v>
@@ -1528,10 +1528,10 @@
         <v>46020</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E43" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1540,7 +1540,7 @@
         <v>1.95</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H43" s="4">
         <v>4</v>
@@ -1554,10 +1554,10 @@
         <v>46020</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E44" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1566,7 +1566,7 @@
         <v>1.6</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H44" s="4">
         <v>4</v>
@@ -1580,10 +1580,10 @@
         <v>46020</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E45" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1592,7 +1592,7 @@
         <v>0.53</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H45" s="4">
         <v>4</v>
@@ -1606,10 +1606,10 @@
         <v>46021</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E46" s="4">
         <v>3</v>
@@ -1618,7 +1618,7 @@
         <v>361</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1629,10 +1629,10 @@
         <v>46021</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E47" s="4">
         <v>3</v>
@@ -1641,7 +1641,7 @@
         <v>210</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1652,10 +1652,10 @@
         <v>46054</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E48" s="4">
         <v>0.2</v>
@@ -1664,7 +1664,7 @@
         <v>66.22</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1675,10 +1675,10 @@
         <v>46054</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E49" s="4">
         <v>0.2</v>
@@ -1687,7 +1687,7 @@
         <v>57.5</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1698,10 +1698,10 @@
         <v>46034</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E50" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1710,7 +1710,7 @@
         <v>1.96</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H50" s="4">
         <v>1</v>
@@ -1724,10 +1724,10 @@
         <v>46034</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E51" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1736,7 +1736,7 @@
         <v>1.31</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H51" s="4">
         <v>1</v>
@@ -1750,10 +1750,10 @@
         <v>46034</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E52" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1762,7 +1762,7 @@
         <v>1.5</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H52" s="4">
         <v>1</v>
@@ -1776,10 +1776,10 @@
         <v>46034</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E53" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1788,7 +1788,7 @@
         <v>0.85</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H53" s="4">
         <v>1</v>
@@ -1802,10 +1802,10 @@
         <v>46034</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E54" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1814,7 +1814,7 @@
         <v>0.88</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H54" s="4">
         <v>1</v>
@@ -1828,10 +1828,10 @@
         <v>46034</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E55" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1840,7 +1840,7 @@
         <v>1.6</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H55" s="4">
         <v>2</v>
@@ -1854,10 +1854,10 @@
         <v>46034</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E56" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1866,7 +1866,7 @@
         <v>1.39</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H56" s="4">
         <v>2</v>
@@ -1880,10 +1880,10 @@
         <v>46034</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E57" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1892,7 +1892,7 @@
         <v>1.28</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H57" s="4">
         <v>2</v>
@@ -1906,10 +1906,10 @@
         <v>46034</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E58" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1918,7 +1918,7 @@
         <v>1.31</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H58" s="4">
         <v>2</v>
@@ -1932,10 +1932,10 @@
         <v>46034</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E59" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1944,7 +1944,7 @@
         <v>1.41</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H59" s="4">
         <v>2</v>
@@ -1958,10 +1958,10 @@
         <v>46034</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E60" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1970,7 +1970,7 @@
         <v>1.25</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H60" s="4">
         <v>3</v>
@@ -1984,10 +1984,10 @@
         <v>46034</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E61" s="4">
         <v>2.5000000000000001E-3</v>
@@ -1996,7 +1996,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H61" s="4">
         <v>3</v>
@@ -2010,10 +2010,10 @@
         <v>46034</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E62" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2022,7 +2022,7 @@
         <v>0.97</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H62" s="4">
         <v>3</v>
@@ -2036,10 +2036,10 @@
         <v>46034</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E63" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2048,7 +2048,7 @@
         <v>1.26</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H63" s="4">
         <v>3</v>
@@ -2062,10 +2062,10 @@
         <v>46034</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E64" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2074,7 +2074,7 @@
         <v>1.83</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H64" s="4">
         <v>4</v>
@@ -2088,10 +2088,10 @@
         <v>46034</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E65" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2100,7 +2100,7 @@
         <v>1.47</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H65" s="4">
         <v>4</v>
@@ -2114,10 +2114,10 @@
         <v>46034</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E66" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2126,7 +2126,7 @@
         <v>1.77</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H66" s="4">
         <v>4</v>
@@ -2140,10 +2140,10 @@
         <v>46034</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E67" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2152,7 +2152,7 @@
         <v>1.45</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H67" s="4">
         <v>4</v>
@@ -2166,10 +2166,10 @@
         <v>46034</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E68" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2178,7 +2178,7 @@
         <v>1.29</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H68" s="4">
         <v>4</v>
@@ -2192,10 +2192,10 @@
         <v>46038</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E69" s="4">
         <v>0.2</v>
@@ -2204,7 +2204,7 @@
         <v>57.45</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2215,10 +2215,10 @@
         <v>46038</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E70" s="4">
         <v>0.2</v>
@@ -2227,7 +2227,7 @@
         <v>37.75</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="71" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2238,10 +2238,10 @@
         <v>46037</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E71" s="4">
         <v>3</v>
@@ -2250,7 +2250,7 @@
         <v>782.3</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="72" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2261,10 +2261,10 @@
         <v>46037</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E72" s="4">
         <v>3</v>
@@ -2273,7 +2273,7 @@
         <v>328.9</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2284,10 +2284,10 @@
         <v>46034</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E73" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2296,7 +2296,7 @@
         <v>1.49</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H73" s="4">
         <v>3</v>
@@ -2310,10 +2310,10 @@
         <v>46048</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E74" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2322,7 +2322,7 @@
         <v>0.49</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H74" s="4">
         <v>1</v>
@@ -2336,10 +2336,10 @@
         <v>46048</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E75" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2348,7 +2348,7 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H75" s="4">
         <v>1</v>
@@ -2362,10 +2362,10 @@
         <v>46048</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E76" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2374,7 +2374,7 @@
         <v>0.1</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H76" s="4">
         <v>1</v>
@@ -2388,10 +2388,10 @@
         <v>46048</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E77" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2400,7 +2400,7 @@
         <v>0.1</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H77" s="4">
         <v>1</v>
@@ -2414,10 +2414,10 @@
         <v>46048</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E78" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2426,7 +2426,7 @@
         <v>0.35</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H78" s="4">
         <v>1</v>
@@ -2440,10 +2440,10 @@
         <v>46048</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E79" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2452,7 +2452,7 @@
         <v>0.9</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H79" s="4">
         <v>2</v>
@@ -2466,10 +2466,10 @@
         <v>46048</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E80" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2478,7 +2478,7 @@
         <v>0.46</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H80" s="4">
         <v>2</v>
@@ -2492,10 +2492,10 @@
         <v>46048</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E81" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2504,7 +2504,7 @@
         <v>0.43</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H81" s="4">
         <v>2</v>
@@ -2518,10 +2518,10 @@
         <v>46048</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E82" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2530,7 +2530,7 @@
         <v>0.84</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H82" s="4">
         <v>2</v>
@@ -2544,10 +2544,10 @@
         <v>46048</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E83" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2556,7 +2556,7 @@
         <v>0.33</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H83" s="4">
         <v>2</v>
@@ -2570,10 +2570,10 @@
         <v>46048</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E84" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2582,7 +2582,7 @@
         <v>0.27</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H84" s="4">
         <v>3</v>
@@ -2596,10 +2596,10 @@
         <v>46048</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E85" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2608,7 +2608,7 @@
         <v>0.23</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H85" s="4">
         <v>3</v>
@@ -2622,10 +2622,10 @@
         <v>46048</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E86" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2634,7 +2634,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H86" s="4">
         <v>3</v>
@@ -2648,10 +2648,10 @@
         <v>46048</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E87" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2660,7 +2660,7 @@
         <v>0.15</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H87" s="4">
         <v>3</v>
@@ -2674,10 +2674,10 @@
         <v>46048</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E88" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2686,7 +2686,7 @@
         <v>0.25</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H88" s="4">
         <v>3</v>
@@ -2700,10 +2700,10 @@
         <v>46048</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E89" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2712,7 +2712,7 @@
         <v>0.4</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H89" s="4">
         <v>4</v>
@@ -2726,10 +2726,10 @@
         <v>46048</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E90" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2738,7 +2738,7 @@
         <v>0.37</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H90" s="4">
         <v>4</v>
@@ -2752,10 +2752,10 @@
         <v>46048</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E91" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2764,7 +2764,7 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H91" s="4">
         <v>4</v>
@@ -2778,10 +2778,10 @@
         <v>46048</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E92" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2790,7 +2790,7 @@
         <v>0.23</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H92" s="4">
         <v>4</v>
@@ -2804,10 +2804,10 @@
         <v>46048</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E93" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2816,7 +2816,7 @@
         <v>1.1599999999999999</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H93" s="4">
         <v>4</v>
@@ -2830,10 +2830,10 @@
         <v>46050</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E94" s="4">
         <v>0.2</v>
@@ -2842,7 +2842,7 @@
         <v>62.59</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="95" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2853,10 +2853,10 @@
         <v>46050</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E95" s="4">
         <v>0.2</v>
@@ -2865,7 +2865,7 @@
         <v>30.87</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="96" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2876,10 +2876,10 @@
         <v>46051</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E96" s="4">
         <v>3</v>
@@ -2888,7 +2888,7 @@
         <v>946.88</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="97" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2899,10 +2899,10 @@
         <v>46051</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E97" s="4">
         <v>3</v>
@@ -2911,7 +2911,7 @@
         <v>575.98</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2922,10 +2922,10 @@
         <v>46063</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E98" s="4">
         <v>0.2</v>
@@ -2934,7 +2934,7 @@
         <v>81.099999999999994</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2945,10 +2945,10 @@
         <v>46063</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E99" s="4">
         <v>0.2</v>
@@ -2957,7 +2957,7 @@
         <v>43.45</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -2968,10 +2968,10 @@
         <v>46062</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E100" s="4">
         <v>2.5000000000000001E-3</v>
@@ -2980,7 +2980,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H100" s="4">
         <v>1</v>
@@ -2994,10 +2994,10 @@
         <v>46062</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E101" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3006,7 +3006,7 @@
         <v>0.23</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H101" s="4">
         <v>1</v>
@@ -3020,10 +3020,10 @@
         <v>46062</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E102" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3032,7 +3032,7 @@
         <v>0.2</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H102" s="4">
         <v>1</v>
@@ -3046,10 +3046,10 @@
         <v>46062</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E103" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3058,7 +3058,7 @@
         <v>0.11</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H103" s="4">
         <v>1</v>
@@ -3072,10 +3072,10 @@
         <v>46062</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E104" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3084,7 +3084,7 @@
         <v>0.36</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H104" s="4">
         <v>1</v>
@@ -3098,10 +3098,10 @@
         <v>46062</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E105" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3110,7 +3110,7 @@
         <v>1.17</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H105" s="4">
         <v>2</v>
@@ -3124,10 +3124,10 @@
         <v>46062</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E106" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3136,7 +3136,7 @@
         <v>0.37</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H106" s="4">
         <v>2</v>
@@ -3150,10 +3150,10 @@
         <v>46062</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E107" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3162,7 +3162,7 @@
         <v>0.49</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H107" s="4">
         <v>2</v>
@@ -3176,10 +3176,10 @@
         <v>46062</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E108" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3188,7 +3188,7 @@
         <v>0.73</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H108" s="4">
         <v>2</v>
@@ -3202,10 +3202,10 @@
         <v>46062</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E109" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3214,7 +3214,7 @@
         <v>0.33</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H109" s="4">
         <v>2</v>
@@ -3228,10 +3228,10 @@
         <v>46062</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E110" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3240,7 +3240,7 @@
         <v>0.34</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H110" s="4">
         <v>3</v>
@@ -3254,10 +3254,10 @@
         <v>46062</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E111" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3266,7 +3266,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H111" s="4">
         <v>3</v>
@@ -3280,10 +3280,10 @@
         <v>46062</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E112" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3292,7 +3292,7 @@
         <v>0.33</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H112" s="4">
         <v>3</v>
@@ -3306,10 +3306,10 @@
         <v>46062</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E113" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3318,7 +3318,7 @@
         <v>0.16</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H113" s="4">
         <v>3</v>
@@ -3332,10 +3332,10 @@
         <v>46062</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E114" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3344,7 +3344,7 @@
         <v>0.19</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H114" s="4">
         <v>3</v>
@@ -3358,10 +3358,10 @@
         <v>46062</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E115" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3370,7 +3370,7 @@
         <v>0.46</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H115" s="4">
         <v>4</v>
@@ -3384,10 +3384,10 @@
         <v>46062</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E116" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3396,7 +3396,7 @@
         <v>0.3</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H116" s="4">
         <v>4</v>
@@ -3410,10 +3410,10 @@
         <v>46062</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E117" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3422,7 +3422,7 @@
         <v>0.44</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H117" s="4">
         <v>4</v>
@@ -3436,10 +3436,10 @@
         <v>46062</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E118" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3448,7 +3448,7 @@
         <v>0.31</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H118" s="4">
         <v>4</v>
@@ -3462,10 +3462,10 @@
         <v>46062</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E119" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3474,7 +3474,7 @@
         <v>0.16</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H119" s="4">
         <v>4</v>
@@ -3488,10 +3488,10 @@
         <v>46071</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E120" s="4">
         <v>3</v>
@@ -3500,7 +3500,7 @@
         <v>1006.679</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3511,10 +3511,10 @@
         <v>46071</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E121" s="4">
         <v>3</v>
@@ -3523,7 +3523,7 @@
         <v>512.19000000000005</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3534,10 +3534,10 @@
         <v>46077</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E122" s="4">
         <v>0.2</v>
@@ -3546,7 +3546,7 @@
         <v>74.05</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3557,10 +3557,10 @@
         <v>46077</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E123" s="4">
         <v>0.2</v>
@@ -3569,7 +3569,7 @@
         <v>45.1</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -3580,10 +3580,10 @@
         <v>46078</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E124" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3592,7 +3592,7 @@
         <v>1.58</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H124" s="4">
         <v>1</v>
@@ -3606,10 +3606,10 @@
         <v>46078</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E125" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3618,7 +3618,7 @@
         <v>1.03</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H125" s="4">
         <v>1</v>
@@ -3632,10 +3632,10 @@
         <v>46078</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E126" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3644,7 +3644,7 @@
         <v>1.02</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H126" s="4">
         <v>1</v>
@@ -3658,10 +3658,10 @@
         <v>46078</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E127" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3670,7 +3670,7 @@
         <v>0.74</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H127" s="4">
         <v>1</v>
@@ -3684,10 +3684,10 @@
         <v>46078</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E128" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3696,7 +3696,7 @@
         <v>1.27</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H128" s="4">
         <v>1</v>
@@ -3710,10 +3710,10 @@
         <v>46078</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E129" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3722,7 +3722,7 @@
         <v>1.65</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H129" s="4">
         <v>2</v>
@@ -3736,10 +3736,10 @@
         <v>46078</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E130" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3748,7 +3748,7 @@
         <v>1.1299999999999999</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H130" s="4">
         <v>2</v>
@@ -3762,10 +3762,10 @@
         <v>46078</v>
       </c>
       <c r="C131" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E131" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3774,7 +3774,7 @@
         <v>0.96</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H131" s="4">
         <v>2</v>
@@ -3788,10 +3788,10 @@
         <v>46078</v>
       </c>
       <c r="C132" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E132" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3800,7 +3800,7 @@
         <v>1.48</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H132" s="4">
         <v>2</v>
@@ -3814,10 +3814,10 @@
         <v>46078</v>
       </c>
       <c r="C133" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E133" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3826,7 +3826,7 @@
         <v>0.41</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H133" s="4">
         <v>2</v>
@@ -3840,10 +3840,10 @@
         <v>46078</v>
       </c>
       <c r="C134" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E134" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3852,7 +3852,7 @@
         <v>0.76</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H134" s="4">
         <v>3</v>
@@ -3866,10 +3866,10 @@
         <v>46078</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E135" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3878,7 +3878,7 @@
         <v>0.75</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H135" s="4">
         <v>3</v>
@@ -3892,10 +3892,10 @@
         <v>46078</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E136" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3904,7 +3904,7 @@
         <v>0.92</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H136" s="4">
         <v>3</v>
@@ -3918,10 +3918,10 @@
         <v>46078</v>
       </c>
       <c r="C137" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E137" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3930,7 +3930,7 @@
         <v>0.39</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H137" s="4">
         <v>3</v>
@@ -3944,10 +3944,10 @@
         <v>46078</v>
       </c>
       <c r="C138" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E138" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3956,7 +3956,7 @@
         <v>0.18</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H138" s="4">
         <v>3</v>
@@ -3970,10 +3970,10 @@
         <v>46078</v>
       </c>
       <c r="C139" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E139" s="4">
         <v>2.5000000000000001E-3</v>
@@ -3982,7 +3982,7 @@
         <v>0.92</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H139" s="4">
         <v>4</v>
@@ -3996,10 +3996,10 @@
         <v>46078</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E140" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4008,7 +4008,7 @@
         <v>1.02</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H140" s="4">
         <v>4</v>
@@ -4022,10 +4022,10 @@
         <v>46078</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E141" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4034,7 +4034,7 @@
         <v>0.69</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H141" s="4">
         <v>4</v>
@@ -4048,10 +4048,10 @@
         <v>46078</v>
       </c>
       <c r="C142" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E142" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4060,7 +4060,7 @@
         <v>0.54</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H142" s="4">
         <v>4</v>
@@ -4074,10 +4074,10 @@
         <v>46078</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E143" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4086,7 +4086,7 @@
         <v>0.19</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H143" s="4">
         <v>4</v>
@@ -4100,10 +4100,10 @@
         <v>46083</v>
       </c>
       <c r="C144" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E144" s="4">
         <v>3</v>
@@ -4112,7 +4112,7 @@
         <v>875.15</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="145" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4123,10 +4123,10 @@
         <v>46083</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E145" s="4">
         <v>3</v>
@@ -4135,7 +4135,7 @@
         <v>628.45000000000005</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="146" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4146,10 +4146,10 @@
         <v>46087</v>
       </c>
       <c r="C146" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E146" s="4">
         <v>0.2</v>
@@ -4158,7 +4158,7 @@
         <v>69.03</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="147" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4169,10 +4169,10 @@
         <v>46087</v>
       </c>
       <c r="C147" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E147" s="4">
         <v>0.2</v>
@@ -4181,7 +4181,7 @@
         <v>46.55</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="148" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4192,10 +4192,10 @@
         <v>46090</v>
       </c>
       <c r="C148" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E148" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4204,7 +4204,7 @@
         <v>1.2</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H148" s="4">
         <v>1</v>
@@ -4218,10 +4218,10 @@
         <v>46090</v>
       </c>
       <c r="C149" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E149" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4230,7 +4230,7 @@
         <v>0.96</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H149" s="4">
         <v>1</v>
@@ -4244,10 +4244,10 @@
         <v>46090</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E150" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4256,7 +4256,7 @@
         <v>1.03</v>
       </c>
       <c r="G150" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H150" s="4">
         <v>1</v>
@@ -4270,10 +4270,10 @@
         <v>46090</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E151" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4282,7 +4282,7 @@
         <v>0.91</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H151" s="4">
         <v>1</v>
@@ -4296,10 +4296,10 @@
         <v>46090</v>
       </c>
       <c r="C152" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E152" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4308,7 +4308,7 @@
         <v>0.91</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H152" s="4">
         <v>1</v>
@@ -4322,10 +4322,10 @@
         <v>46090</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E153" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4334,7 +4334,7 @@
         <v>0.6</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H153" s="4">
         <v>1</v>
@@ -4348,10 +4348,10 @@
         <v>46090</v>
       </c>
       <c r="C154" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E154" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4360,7 +4360,7 @@
         <v>0.98</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H154" s="4">
         <v>2</v>
@@ -4374,10 +4374,10 @@
         <v>46090</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E155" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4386,7 +4386,7 @@
         <v>0.87</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H155" s="4">
         <v>2</v>
@@ -4400,10 +4400,10 @@
         <v>46090</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E156" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4412,7 +4412,7 @@
         <v>0.83</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H156" s="4">
         <v>2</v>
@@ -4426,10 +4426,10 @@
         <v>46090</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E157" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4438,7 +4438,7 @@
         <v>0.97</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H157" s="4">
         <v>2</v>
@@ -4452,10 +4452,10 @@
         <v>46090</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E158" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4464,7 +4464,7 @@
         <v>0.53</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H158" s="4">
         <v>2</v>
@@ -4478,10 +4478,10 @@
         <v>46090</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E159" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4490,7 +4490,7 @@
         <v>0.72</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H159" s="4">
         <v>3</v>
@@ -4504,10 +4504,10 @@
         <v>46090</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E160" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4516,7 +4516,7 @@
         <v>0.6</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H160" s="4">
         <v>3</v>
@@ -4530,10 +4530,10 @@
         <v>46090</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E161" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4542,7 +4542,7 @@
         <v>0.8</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H161" s="4">
         <v>3</v>
@@ -4556,10 +4556,10 @@
         <v>46090</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E162" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4568,7 +4568,7 @@
         <v>0.81</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H162" s="4">
         <v>3</v>
@@ -4582,10 +4582,10 @@
         <v>46090</v>
       </c>
       <c r="C163" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E163" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4594,7 +4594,7 @@
         <v>0.2</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H163" s="4">
         <v>3</v>
@@ -4608,10 +4608,10 @@
         <v>46090</v>
       </c>
       <c r="C164" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E164" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4620,7 +4620,7 @@
         <v>0.6</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H164" s="4">
         <v>4</v>
@@ -4634,10 +4634,10 @@
         <v>46090</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E165" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4646,7 +4646,7 @@
         <v>0.77</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H165" s="4">
         <v>4</v>
@@ -4660,10 +4660,10 @@
         <v>46090</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E166" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4672,7 +4672,7 @@
         <v>0.66</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H166" s="4">
         <v>4</v>
@@ -4686,10 +4686,10 @@
         <v>46090</v>
       </c>
       <c r="C167" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E167" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4698,7 +4698,7 @@
         <v>0.5</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H167" s="4">
         <v>4</v>
@@ -4712,10 +4712,10 @@
         <v>46090</v>
       </c>
       <c r="C168" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E168" s="4">
         <v>2.5000000000000001E-3</v>
@@ -4724,7 +4724,7 @@
         <v>0.13</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H168" s="4">
         <v>4</v>
@@ -4738,10 +4738,10 @@
         <v>46094</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E169" s="4">
         <v>3</v>
@@ -4750,7 +4750,7 @@
         <v>573.74</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4761,10 +4761,10 @@
         <v>46094</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E170" s="4">
         <v>3</v>
@@ -4773,7 +4773,7 @@
         <v>397.8</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="171" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4784,10 +4784,10 @@
         <v>46097</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E171" s="4">
         <v>0.2</v>
@@ -4796,7 +4796,7 @@
         <v>98.9</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="172" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4807,10 +4807,10 @@
         <v>46097</v>
       </c>
       <c r="C172" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E172" s="4">
         <v>0.2</v>
@@ -4819,7 +4819,7 @@
         <v>74.55</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4830,10 +4830,10 @@
         <v>46104</v>
       </c>
       <c r="C173" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E173" s="4">
         <v>3</v>
@@ -4842,7 +4842,7 @@
         <v>556.79999999999995</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="174" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4853,10 +4853,10 @@
         <v>46104</v>
       </c>
       <c r="C174" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E174" s="4">
         <v>3</v>
@@ -4865,7 +4865,7 @@
         <v>352.4</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="175" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4876,10 +4876,10 @@
         <v>46106</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E175" s="4">
         <v>0.2</v>
@@ -4888,7 +4888,7 @@
         <v>88.85</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="176" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4899,10 +4899,10 @@
         <v>46106</v>
       </c>
       <c r="C176" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E176" s="4">
         <v>0.2</v>
@@ -4911,7 +4911,7 @@
         <v>60.9</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="177" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4922,10 +4922,10 @@
         <v>46114</v>
       </c>
       <c r="C177" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E177" s="4">
         <v>3</v>
@@ -4934,7 +4934,7 @@
         <v>532.4</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4945,10 +4945,10 @@
         <v>46114</v>
       </c>
       <c r="C178" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E178" s="4">
         <v>3</v>
@@ -4957,7 +4957,7 @@
         <v>328.6</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="179" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4968,10 +4968,10 @@
         <v>46115</v>
       </c>
       <c r="C179" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E179" s="4">
         <v>0.2</v>
@@ -4980,7 +4980,7 @@
         <v>73.81</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="180" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -4991,10 +4991,10 @@
         <v>46115</v>
       </c>
       <c r="C180" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E180" s="4">
         <v>0.2</v>
@@ -5003,7 +5003,7 @@
         <v>50.2</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="181" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5014,10 +5014,10 @@
         <v>46125</v>
       </c>
       <c r="C181" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E181" s="4">
         <v>0.2</v>
@@ -5026,7 +5026,7 @@
         <v>83.7</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="182" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5037,10 +5037,10 @@
         <v>46125</v>
       </c>
       <c r="C182" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E182" s="4">
         <v>0.2</v>
@@ -5049,7 +5049,7 @@
         <v>57.25</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="183" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5060,10 +5060,10 @@
         <v>46123</v>
       </c>
       <c r="C183" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E183" s="4">
         <v>3</v>
@@ -5072,7 +5072,7 @@
         <v>569</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="184" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5083,10 +5083,10 @@
         <v>46123</v>
       </c>
       <c r="C184" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E184" s="4">
         <v>3</v>
@@ -5095,7 +5095,7 @@
         <v>386.7</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5106,10 +5106,10 @@
         <v>46100</v>
       </c>
       <c r="C185" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E185" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5118,7 +5118,7 @@
         <v>1.2</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H185" s="4">
         <v>1</v>
@@ -5132,10 +5132,10 @@
         <v>46100</v>
       </c>
       <c r="C186" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E186" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5144,7 +5144,7 @@
         <v>0.97</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H186" s="4">
         <v>1</v>
@@ -5158,10 +5158,10 @@
         <v>46100</v>
       </c>
       <c r="C187" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E187" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5170,7 +5170,7 @@
         <v>1.19</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H187" s="4">
         <v>1</v>
@@ -5184,10 +5184,10 @@
         <v>46100</v>
       </c>
       <c r="C188" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E188" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5196,7 +5196,7 @@
         <v>0.87</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H188" s="4">
         <v>1</v>
@@ -5210,10 +5210,10 @@
         <v>46100</v>
       </c>
       <c r="C189" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E189" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5222,7 +5222,7 @@
         <v>0.84</v>
       </c>
       <c r="G189" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H189" s="4">
         <v>1</v>
@@ -5236,10 +5236,10 @@
         <v>46100</v>
       </c>
       <c r="C190" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E190" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5248,7 +5248,7 @@
         <v>1.25</v>
       </c>
       <c r="G190" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H190" s="4">
         <v>2</v>
@@ -5262,10 +5262,10 @@
         <v>46100</v>
       </c>
       <c r="C191" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E191" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5274,7 +5274,7 @@
         <v>0.84</v>
       </c>
       <c r="G191" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H191" s="4">
         <v>2</v>
@@ -5288,10 +5288,10 @@
         <v>46100</v>
       </c>
       <c r="C192" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E192" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5300,7 +5300,7 @@
         <v>0.99</v>
       </c>
       <c r="G192" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H192" s="4">
         <v>2</v>
@@ -5314,10 +5314,10 @@
         <v>46100</v>
       </c>
       <c r="C193" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E193" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5326,7 +5326,7 @@
         <v>1.25</v>
       </c>
       <c r="G193" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H193" s="4">
         <v>2</v>
@@ -5340,10 +5340,10 @@
         <v>46100</v>
       </c>
       <c r="C194" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E194" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5352,7 +5352,7 @@
         <v>0.72</v>
       </c>
       <c r="G194" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H194" s="4">
         <v>2</v>
@@ -5366,10 +5366,10 @@
         <v>46100</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E195" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5378,7 +5378,7 @@
         <v>0.94</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H195" s="4">
         <v>3</v>
@@ -5392,10 +5392,10 @@
         <v>46100</v>
       </c>
       <c r="C196" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E196" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5404,7 +5404,7 @@
         <v>0.88</v>
       </c>
       <c r="G196" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H196" s="4">
         <v>3</v>
@@ -5418,10 +5418,10 @@
         <v>46100</v>
       </c>
       <c r="C197" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E197" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5430,7 +5430,7 @@
         <v>0.87</v>
       </c>
       <c r="G197" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H197" s="4">
         <v>3</v>
@@ -5444,10 +5444,10 @@
         <v>46100</v>
       </c>
       <c r="C198" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E198" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5456,7 +5456,7 @@
         <v>0.88</v>
       </c>
       <c r="G198" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H198" s="4">
         <v>3</v>
@@ -5470,10 +5470,10 @@
         <v>46100</v>
       </c>
       <c r="C199" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E199" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5482,7 +5482,7 @@
         <v>0.32</v>
       </c>
       <c r="G199" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H199" s="4">
         <v>3</v>
@@ -5496,10 +5496,10 @@
         <v>46100</v>
       </c>
       <c r="C200" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E200" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5508,7 +5508,7 @@
         <v>0.95</v>
       </c>
       <c r="G200" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H200" s="4">
         <v>4</v>
@@ -5522,10 +5522,10 @@
         <v>46100</v>
       </c>
       <c r="C201" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E201" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5534,7 +5534,7 @@
         <v>0.78</v>
       </c>
       <c r="G201" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H201" s="4">
         <v>4</v>
@@ -5548,10 +5548,10 @@
         <v>46100</v>
       </c>
       <c r="C202" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E202" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5560,7 +5560,7 @@
         <v>0.88</v>
       </c>
       <c r="G202" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H202" s="4">
         <v>4</v>
@@ -5574,10 +5574,10 @@
         <v>46100</v>
       </c>
       <c r="C203" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E203" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5586,7 +5586,7 @@
         <v>0.5</v>
       </c>
       <c r="G203" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H203" s="4">
         <v>4</v>
@@ -5600,10 +5600,10 @@
         <v>46100</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E204" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5612,7 +5612,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="G204" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H204" s="4">
         <v>4</v>
@@ -5626,10 +5626,10 @@
         <v>46136</v>
       </c>
       <c r="C205" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E205" s="4">
         <v>0.2</v>
@@ -5638,7 +5638,7 @@
         <v>82.4</v>
       </c>
       <c r="G205" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="206" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5649,10 +5649,10 @@
         <v>46136</v>
       </c>
       <c r="C206" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E206" s="4">
         <v>0.2</v>
@@ -5661,7 +5661,7 @@
         <v>47.13</v>
       </c>
       <c r="G206" s="4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="207" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5672,10 +5672,10 @@
         <v>46136</v>
       </c>
       <c r="C207" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E207" s="4">
         <v>3</v>
@@ -5684,7 +5684,7 @@
         <v>893.9</v>
       </c>
       <c r="G207" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="208" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5695,10 +5695,10 @@
         <v>46136</v>
       </c>
       <c r="C208" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E208" s="4">
         <v>3</v>
@@ -5707,7 +5707,7 @@
         <v>520.5</v>
       </c>
       <c r="G208" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="209" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -5718,10 +5718,10 @@
         <v>46108</v>
       </c>
       <c r="C209" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E209" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5730,7 +5730,7 @@
         <v>0.46</v>
       </c>
       <c r="G209" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H209" s="4">
         <v>1</v>
@@ -5744,10 +5744,10 @@
         <v>46108</v>
       </c>
       <c r="C210" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E210" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5756,7 +5756,7 @@
         <v>0.4</v>
       </c>
       <c r="G210" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H210" s="4">
         <v>1</v>
@@ -5770,10 +5770,10 @@
         <v>46108</v>
       </c>
       <c r="C211" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E211" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5782,7 +5782,7 @@
         <v>0.46</v>
       </c>
       <c r="G211" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H211" s="4">
         <v>1</v>
@@ -5796,10 +5796,10 @@
         <v>46108</v>
       </c>
       <c r="C212" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E212" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5808,7 +5808,7 @@
         <v>0.43</v>
       </c>
       <c r="G212" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H212" s="4">
         <v>1</v>
@@ -5822,10 +5822,10 @@
         <v>46108</v>
       </c>
       <c r="C213" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E213" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5834,7 +5834,7 @@
         <v>0.39</v>
       </c>
       <c r="G213" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H213" s="4">
         <v>1</v>
@@ -5848,10 +5848,10 @@
         <v>46108</v>
       </c>
       <c r="C214" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D214" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E214" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5860,7 +5860,7 @@
         <v>0.7</v>
       </c>
       <c r="G214" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H214" s="4">
         <v>2</v>
@@ -5874,10 +5874,10 @@
         <v>46108</v>
       </c>
       <c r="C215" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D215" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E215" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5886,7 +5886,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G215" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H215" s="4">
         <v>2</v>
@@ -5900,10 +5900,10 @@
         <v>46108</v>
       </c>
       <c r="C216" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D216" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E216" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5912,7 +5912,7 @@
         <v>0.39</v>
       </c>
       <c r="G216" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H216" s="4">
         <v>2</v>
@@ -5926,10 +5926,10 @@
         <v>46108</v>
       </c>
       <c r="C217" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D217" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E217" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5938,7 +5938,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="G217" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H217" s="4">
         <v>2</v>
@@ -5952,10 +5952,10 @@
         <v>46108</v>
       </c>
       <c r="C218" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D218" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E218" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5964,7 +5964,7 @@
         <v>0.35</v>
       </c>
       <c r="G218" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H218" s="4">
         <v>2</v>
@@ -5978,10 +5978,10 @@
         <v>46108</v>
       </c>
       <c r="C219" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D219" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E219" s="4">
         <v>2.5000000000000001E-3</v>
@@ -5990,7 +5990,7 @@
         <v>0.5</v>
       </c>
       <c r="G219" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H219" s="4">
         <v>3</v>
@@ -6004,10 +6004,10 @@
         <v>46108</v>
       </c>
       <c r="C220" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D220" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E220" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6016,7 +6016,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="G220" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H220" s="4">
         <v>3</v>
@@ -6030,10 +6030,10 @@
         <v>46108</v>
       </c>
       <c r="C221" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D221" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E221" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6042,7 +6042,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G221" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H221" s="4">
         <v>3</v>
@@ -6056,10 +6056,10 @@
         <v>46108</v>
       </c>
       <c r="C222" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D222" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E222" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6068,7 +6068,7 @@
         <v>0.47</v>
       </c>
       <c r="G222" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H222" s="4">
         <v>3</v>
@@ -6082,10 +6082,10 @@
         <v>46108</v>
       </c>
       <c r="C223" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D223" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E223" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6094,7 +6094,7 @@
         <v>0.42</v>
       </c>
       <c r="G223" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H223" s="4">
         <v>3</v>
@@ -6108,10 +6108,10 @@
         <v>46108</v>
       </c>
       <c r="C224" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D224" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E224" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6120,7 +6120,7 @@
         <v>0.53</v>
       </c>
       <c r="G224" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H224" s="4">
         <v>4</v>
@@ -6134,10 +6134,10 @@
         <v>46108</v>
       </c>
       <c r="C225" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D225" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E225" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6146,7 +6146,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="G225" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H225" s="4">
         <v>4</v>
@@ -6160,10 +6160,10 @@
         <v>46108</v>
       </c>
       <c r="C226" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D226" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E226" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6172,7 +6172,7 @@
         <v>0.49</v>
       </c>
       <c r="G226" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H226" s="4">
         <v>4</v>
@@ -6186,10 +6186,10 @@
         <v>46108</v>
       </c>
       <c r="C227" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D227" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E227" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6198,7 +6198,7 @@
         <v>0.48</v>
       </c>
       <c r="G227" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H227" s="4">
         <v>4</v>
@@ -6212,10 +6212,10 @@
         <v>46108</v>
       </c>
       <c r="C228" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E228" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6224,7 +6224,7 @@
         <v>0.27</v>
       </c>
       <c r="G228" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H228" s="4">
         <v>4</v>
@@ -6238,10 +6238,10 @@
         <v>46118</v>
       </c>
       <c r="C229" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E229" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6250,7 +6250,7 @@
         <v>0.99</v>
       </c>
       <c r="G229" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H229" s="4">
         <v>1</v>
@@ -6264,10 +6264,10 @@
         <v>46118</v>
       </c>
       <c r="C230" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E230" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6276,7 +6276,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="G230" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H230" s="4">
         <v>1</v>
@@ -6290,10 +6290,10 @@
         <v>46118</v>
       </c>
       <c r="C231" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E231" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6302,7 +6302,7 @@
         <v>0.64</v>
       </c>
       <c r="G231" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H231" s="4">
         <v>1</v>
@@ -6316,10 +6316,10 @@
         <v>46118</v>
       </c>
       <c r="C232" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E232" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6328,7 +6328,7 @@
         <v>0.68</v>
       </c>
       <c r="G232" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H232" s="4">
         <v>1</v>
@@ -6342,10 +6342,10 @@
         <v>46118</v>
       </c>
       <c r="C233" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D233" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E233" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6354,7 +6354,7 @@
         <v>0.49</v>
       </c>
       <c r="G233" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H233" s="4">
         <v>1</v>
@@ -6368,10 +6368,10 @@
         <v>46118</v>
       </c>
       <c r="C234" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D234" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E234" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6380,7 +6380,7 @@
         <v>1.2</v>
       </c>
       <c r="G234" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H234" s="4">
         <v>2</v>
@@ -6394,10 +6394,10 @@
         <v>46118</v>
       </c>
       <c r="C235" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E235" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6406,7 +6406,7 @@
         <v>0.87</v>
       </c>
       <c r="G235" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H235" s="4">
         <v>2</v>
@@ -6420,10 +6420,10 @@
         <v>46118</v>
       </c>
       <c r="C236" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D236" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E236" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6432,7 +6432,7 @@
         <v>0.88</v>
       </c>
       <c r="G236" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H236" s="4">
         <v>2</v>
@@ -6446,10 +6446,10 @@
         <v>46118</v>
       </c>
       <c r="C237" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D237" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E237" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6458,7 +6458,7 @@
         <v>1.02</v>
       </c>
       <c r="G237" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H237" s="4">
         <v>2</v>
@@ -6472,10 +6472,10 @@
         <v>46118</v>
       </c>
       <c r="C238" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E238" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6484,7 +6484,7 @@
         <v>0.68</v>
       </c>
       <c r="G238" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H238" s="4">
         <v>2</v>
@@ -6498,10 +6498,10 @@
         <v>46118</v>
       </c>
       <c r="C239" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D239" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E239" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6510,7 +6510,7 @@
         <v>0.88</v>
       </c>
       <c r="G239" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H239" s="4">
         <v>3</v>
@@ -6524,10 +6524,10 @@
         <v>46118</v>
       </c>
       <c r="C240" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D240" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E240" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6536,7 +6536,7 @@
         <v>0.83</v>
       </c>
       <c r="G240" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H240" s="4">
         <v>3</v>
@@ -6550,10 +6550,10 @@
         <v>46118</v>
       </c>
       <c r="C241" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D241" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E241" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6562,7 +6562,7 @@
         <v>0.89</v>
       </c>
       <c r="G241" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H241" s="4">
         <v>3</v>
@@ -6576,10 +6576,10 @@
         <v>46118</v>
       </c>
       <c r="C242" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D242" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E242" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6588,7 +6588,7 @@
         <v>0.62</v>
       </c>
       <c r="G242" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H242" s="4">
         <v>3</v>
@@ -6602,10 +6602,10 @@
         <v>46118</v>
       </c>
       <c r="C243" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D243" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E243" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6614,7 +6614,7 @@
         <v>0.59</v>
       </c>
       <c r="G243" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H243" s="4">
         <v>3</v>
@@ -6628,10 +6628,10 @@
         <v>46118</v>
       </c>
       <c r="C244" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D244" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E244" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6640,7 +6640,7 @@
         <v>0.83</v>
       </c>
       <c r="G244" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H244" s="4">
         <v>4</v>
@@ -6654,10 +6654,10 @@
         <v>46118</v>
       </c>
       <c r="C245" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D245" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E245" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6666,7 +6666,7 @@
         <v>0.51</v>
       </c>
       <c r="G245" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H245" s="4">
         <v>4</v>
@@ -6680,10 +6680,10 @@
         <v>46118</v>
       </c>
       <c r="C246" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D246" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E246" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6692,7 +6692,7 @@
         <v>0.65</v>
       </c>
       <c r="G246" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H246" s="4">
         <v>4</v>
@@ -6706,10 +6706,10 @@
         <v>46118</v>
       </c>
       <c r="C247" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D247" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E247" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6718,7 +6718,7 @@
         <v>0.66</v>
       </c>
       <c r="G247" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H247" s="4">
         <v>4</v>
@@ -6732,10 +6732,10 @@
         <v>46118</v>
       </c>
       <c r="C248" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E248" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6744,7 +6744,7 @@
         <v>0.38</v>
       </c>
       <c r="G248" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H248" s="4">
         <v>4</v>
@@ -6758,10 +6758,10 @@
         <v>46126</v>
       </c>
       <c r="C249" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E249" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6770,7 +6770,7 @@
         <v>0.81</v>
       </c>
       <c r="G249" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H249" s="4">
         <v>1</v>
@@ -6784,10 +6784,10 @@
         <v>46126</v>
       </c>
       <c r="C250" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D250" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E250" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6796,7 +6796,7 @@
         <v>0.5</v>
       </c>
       <c r="G250" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H250" s="4">
         <v>1</v>
@@ -6810,10 +6810,10 @@
         <v>46126</v>
       </c>
       <c r="C251" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E251" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6822,7 +6822,7 @@
         <v>0.45</v>
       </c>
       <c r="G251" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H251" s="4">
         <v>1</v>
@@ -6836,10 +6836,10 @@
         <v>46126</v>
       </c>
       <c r="C252" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E252" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6848,7 +6848,7 @@
         <v>0.34</v>
       </c>
       <c r="G252" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H252" s="4">
         <v>1</v>
@@ -6862,10 +6862,10 @@
         <v>46126</v>
       </c>
       <c r="C253" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D253" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E253" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6874,7 +6874,7 @@
         <v>0.38</v>
       </c>
       <c r="G253" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H253" s="4">
         <v>1</v>
@@ -6888,10 +6888,10 @@
         <v>46126</v>
       </c>
       <c r="C254" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D254" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E254" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6900,7 +6900,7 @@
         <v>1.07</v>
       </c>
       <c r="G254" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H254" s="4">
         <v>2</v>
@@ -6914,10 +6914,10 @@
         <v>46126</v>
       </c>
       <c r="C255" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D255" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E255" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6926,7 +6926,7 @@
         <v>0.62</v>
       </c>
       <c r="G255" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H255" s="4">
         <v>2</v>
@@ -6940,10 +6940,10 @@
         <v>46126</v>
       </c>
       <c r="C256" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D256" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E256" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6952,7 +6952,7 @@
         <v>0.54</v>
       </c>
       <c r="G256" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H256" s="4">
         <v>2</v>
@@ -6966,10 +6966,10 @@
         <v>46126</v>
       </c>
       <c r="C257" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D257" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E257" s="4">
         <v>2.5000000000000001E-3</v>
@@ -6978,7 +6978,7 @@
         <v>0.68</v>
       </c>
       <c r="G257" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H257" s="4">
         <v>2</v>
@@ -6992,10 +6992,10 @@
         <v>46126</v>
       </c>
       <c r="C258" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D258" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E258" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7004,7 +7004,7 @@
         <v>0.44</v>
       </c>
       <c r="G258" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H258" s="4">
         <v>2</v>
@@ -7018,10 +7018,10 @@
         <v>46126</v>
       </c>
       <c r="C259" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D259" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E259" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7030,7 +7030,7 @@
         <v>0.77</v>
       </c>
       <c r="G259" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H259" s="4">
         <v>3</v>
@@ -7044,10 +7044,10 @@
         <v>46126</v>
       </c>
       <c r="C260" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D260" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E260" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7056,7 +7056,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="G260" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H260" s="4">
         <v>3</v>
@@ -7070,10 +7070,10 @@
         <v>46126</v>
       </c>
       <c r="C261" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D261" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E261" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7082,7 +7082,7 @@
         <v>0.62</v>
       </c>
       <c r="G261" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H261" s="4">
         <v>3</v>
@@ -7096,10 +7096,10 @@
         <v>46126</v>
       </c>
       <c r="C262" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D262" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E262" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7108,7 +7108,7 @@
         <v>0.82</v>
       </c>
       <c r="G262" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H262" s="4">
         <v>3</v>
@@ -7122,10 +7122,10 @@
         <v>46126</v>
       </c>
       <c r="C263" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D263" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E263" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7134,7 +7134,7 @@
         <v>0.61</v>
       </c>
       <c r="G263" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H263" s="4">
         <v>3</v>
@@ -7148,10 +7148,10 @@
         <v>46126</v>
       </c>
       <c r="C264" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D264" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E264" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7160,7 +7160,7 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="G264" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H264" s="4">
         <v>4</v>
@@ -7174,10 +7174,10 @@
         <v>46126</v>
       </c>
       <c r="C265" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E265" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7186,7 +7186,7 @@
         <v>0.48</v>
       </c>
       <c r="G265" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H265" s="4">
         <v>4</v>
@@ -7200,10 +7200,10 @@
         <v>46126</v>
       </c>
       <c r="C266" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D266" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E266" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7212,7 +7212,7 @@
         <v>0.49</v>
       </c>
       <c r="G266" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H266" s="4">
         <v>4</v>
@@ -7226,10 +7226,10 @@
         <v>46126</v>
       </c>
       <c r="C267" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D267" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E267" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7238,7 +7238,7 @@
         <v>0.54</v>
       </c>
       <c r="G267" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H267" s="4">
         <v>4</v>
@@ -7252,10 +7252,10 @@
         <v>46126</v>
       </c>
       <c r="C268" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E268" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7264,7 +7264,7 @@
         <v>0.32</v>
       </c>
       <c r="G268" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H268" s="4">
         <v>4</v>
@@ -7278,10 +7278,10 @@
         <v>46136</v>
       </c>
       <c r="C269" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E269" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7290,7 +7290,7 @@
         <v>1.06</v>
       </c>
       <c r="G269" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H269" s="4">
         <v>1</v>
@@ -7304,10 +7304,10 @@
         <v>46136</v>
       </c>
       <c r="C270" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D270" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E270" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7316,7 +7316,7 @@
         <v>0.53</v>
       </c>
       <c r="G270" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H270" s="4">
         <v>1</v>
@@ -7330,10 +7330,10 @@
         <v>46136</v>
       </c>
       <c r="C271" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E271" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7342,7 +7342,7 @@
         <v>0.53</v>
       </c>
       <c r="G271" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H271" s="4">
         <v>1</v>
@@ -7356,10 +7356,10 @@
         <v>46136</v>
       </c>
       <c r="C272" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E272" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7368,7 +7368,7 @@
         <v>0.45</v>
       </c>
       <c r="G272" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H272" s="4">
         <v>1</v>
@@ -7382,10 +7382,10 @@
         <v>46136</v>
       </c>
       <c r="C273" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E273" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7394,7 +7394,7 @@
         <v>0.47</v>
       </c>
       <c r="G273" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H273" s="4">
         <v>1</v>
@@ -7408,10 +7408,10 @@
         <v>46136</v>
       </c>
       <c r="C274" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E274" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7420,7 +7420,7 @@
         <v>1</v>
       </c>
       <c r="G274" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H274" s="4">
         <v>2</v>
@@ -7434,10 +7434,10 @@
         <v>46136</v>
       </c>
       <c r="C275" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D275" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E275" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7446,7 +7446,7 @@
         <v>0.45</v>
       </c>
       <c r="G275" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H275" s="4">
         <v>2</v>
@@ -7460,10 +7460,10 @@
         <v>46136</v>
       </c>
       <c r="C276" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E276" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7472,7 +7472,7 @@
         <v>0.71</v>
       </c>
       <c r="G276" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H276" s="4">
         <v>2</v>
@@ -7486,10 +7486,10 @@
         <v>46136</v>
       </c>
       <c r="C277" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E277" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7498,7 +7498,7 @@
         <v>0.75</v>
       </c>
       <c r="G277" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H277" s="4">
         <v>2</v>
@@ -7512,10 +7512,10 @@
         <v>46136</v>
       </c>
       <c r="C278" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E278" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7524,7 +7524,7 @@
         <v>0.41</v>
       </c>
       <c r="G278" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H278" s="4">
         <v>2</v>
@@ -7538,10 +7538,10 @@
         <v>46136</v>
       </c>
       <c r="C279" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E279" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7550,7 +7550,7 @@
         <v>0.52</v>
       </c>
       <c r="G279" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H279" s="4">
         <v>3</v>
@@ -7564,10 +7564,10 @@
         <v>46136</v>
       </c>
       <c r="C280" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D280" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E280" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7576,7 +7576,7 @@
         <v>0.65</v>
       </c>
       <c r="G280" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H280" s="4">
         <v>3</v>
@@ -7590,10 +7590,10 @@
         <v>46136</v>
       </c>
       <c r="C281" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E281" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7602,7 +7602,7 @@
         <v>0.71</v>
       </c>
       <c r="G281" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H281" s="4">
         <v>3</v>
@@ -7616,10 +7616,10 @@
         <v>46136</v>
       </c>
       <c r="C282" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E282" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7628,7 +7628,7 @@
         <v>0.62</v>
       </c>
       <c r="G282" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H282" s="4">
         <v>3</v>
@@ -7642,10 +7642,10 @@
         <v>46136</v>
       </c>
       <c r="C283" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D283" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E283" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7654,7 +7654,7 @@
         <v>0.37</v>
       </c>
       <c r="G283" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H283" s="4">
         <v>3</v>
@@ -7668,10 +7668,10 @@
         <v>46136</v>
       </c>
       <c r="C284" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D284" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E284" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7680,7 +7680,7 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="G284" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H284" s="4">
         <v>4</v>
@@ -7694,10 +7694,10 @@
         <v>46136</v>
       </c>
       <c r="C285" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D285" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E285" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7706,7 +7706,7 @@
         <v>0.49</v>
       </c>
       <c r="G285" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H285" s="4">
         <v>4</v>
@@ -7720,10 +7720,10 @@
         <v>46136</v>
       </c>
       <c r="C286" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D286" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E286" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7732,7 +7732,7 @@
         <v>0.61</v>
       </c>
       <c r="G286" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H286" s="4">
         <v>4</v>
@@ -7746,10 +7746,10 @@
         <v>46136</v>
       </c>
       <c r="C287" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E287" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7758,7 +7758,7 @@
         <v>0.66</v>
       </c>
       <c r="G287" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H287" s="4">
         <v>4</v>
@@ -7772,10 +7772,10 @@
         <v>46136</v>
       </c>
       <c r="C288" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E288" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7784,7 +7784,7 @@
         <v>0.46</v>
       </c>
       <c r="G288" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H288" s="4">
         <v>4</v>
@@ -7798,10 +7798,10 @@
         <v>46144</v>
       </c>
       <c r="C289" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E289" s="4">
         <v>0.2</v>
@@ -7810,7 +7810,7 @@
         <v>68.2</v>
       </c>
       <c r="G289" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="290" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -7821,10 +7821,10 @@
         <v>46144</v>
       </c>
       <c r="C290" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E290" s="4">
         <v>0.2</v>
@@ -7833,7 +7833,7 @@
         <v>51.55</v>
       </c>
       <c r="G290" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="291" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -7844,10 +7844,10 @@
         <v>46146</v>
       </c>
       <c r="C291" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E291" s="4">
         <v>3</v>
@@ -7856,7 +7856,7 @@
         <v>830.1</v>
       </c>
       <c r="G291" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="292" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -7867,10 +7867,10 @@
         <v>46146</v>
       </c>
       <c r="C292" s="4" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E292" s="4">
         <v>3</v>
@@ -7879,7 +7879,7 @@
         <v>547.6</v>
       </c>
       <c r="G292" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="293" spans="1:8" ht="22.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -7890,10 +7890,10 @@
         <v>46146</v>
       </c>
       <c r="C293" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E293" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7902,7 +7902,7 @@
         <v>1</v>
       </c>
       <c r="G293" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H293" s="4">
         <v>1</v>
@@ -7916,10 +7916,10 @@
         <v>46146</v>
       </c>
       <c r="C294" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D294" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E294" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7928,7 +7928,7 @@
         <v>0.71</v>
       </c>
       <c r="G294" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H294" s="4">
         <v>1</v>
@@ -7942,10 +7942,10 @@
         <v>46146</v>
       </c>
       <c r="C295" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D295" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E295" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7954,7 +7954,7 @@
         <v>0.83</v>
       </c>
       <c r="G295" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H295" s="4">
         <v>1</v>
@@ -7968,10 +7968,10 @@
         <v>46146</v>
       </c>
       <c r="C296" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E296" s="4">
         <v>2.5000000000000001E-3</v>
@@ -7980,7 +7980,7 @@
         <v>0.56000000000000005</v>
       </c>
       <c r="G296" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H296" s="4">
         <v>1</v>
@@ -7994,10 +7994,10 @@
         <v>46146</v>
       </c>
       <c r="C297" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E297" s="4">
         <v>2.5000000000000001E-3</v>
@@ -8006,7 +8006,7 @@
         <v>0.3</v>
       </c>
       <c r="G297" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H297" s="4">
         <v>1</v>
@@ -8020,10 +8020,10 @@
         <v>46146</v>
       </c>
       <c r="C298" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D298" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E298" s="4">
         <v>2.5000000000000001E-3</v>
@@ -8032,7 +8032,7 @@
         <v>0.9</v>
       </c>
       <c r="G298" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H298" s="4">
         <v>2</v>
@@ -8046,10 +8046,10 @@
         <v>46146</v>
       </c>
       <c r="C299" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D299" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E299" s="4">
         <v>2.5000000000000001E-3</v>
@@ -8058,7 +8058,7 @@
         <v>0.77</v>
       </c>
       <c r="G299" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H299" s="4">
         <v>2</v>
@@ -8072,10 +8072,10 @@
         <v>46146</v>
       </c>
       <c r="C300" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D300" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E300" s="4">
         <v>2.5000000000000001E-3</v>
@@ -8084,7 +8084,7 @@
         <v>0.56999999999999995</v>
       </c>
       <c r="G300" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H300" s="4">
         <v>2</v>
@@ -8098,10 +8098,10 @@
         <v>46146</v>
       </c>
       <c r="C301" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D301" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E301" s="4">
         <v>2.5000000000000001E-3</v>
@@ -8110,7 +8110,7 @@
         <v>0.9</v>
       </c>
       <c r="G301" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H301" s="4">
         <v>2</v>
@@ -8124,10 +8124,10 @@
         <v>46146</v>
       </c>
       <c r="C302" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E302" s="4">
         <v>2.5000000000000001E-3</v>
@@ -8136,7 +8136,7 @@
         <v>0.21</v>
       </c>
       <c r="G302" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H302" s="4">
         <v>2</v>
@@ -8150,10 +8150,10 @@
         <v>46146</v>
       </c>
       <c r="C303" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D303" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E303" s="4">
         <v>2.5000000000000001E-3</v>
@@ -8162,7 +8162,7 @@
         <v>0.69</v>
       </c>
       <c r="G303" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H303" s="4">
         <v>3</v>
@@ -8176,10 +8176,10 @@
         <v>46146</v>
       </c>
       <c r="C304" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D304" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E304" s="4">
         <v>2.5000000000000001E-3</v>
@@ -8188,7 +8188,7 @@
         <v>0.39</v>
       </c>
       <c r="G304" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H304" s="4">
         <v>3</v>
@@ -8202,10 +8202,10 @@
         <v>46146</v>
       </c>
       <c r="C305" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D305" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E305" s="4">
         <v>2.5000000000000001E-3</v>
@@ -8214,7 +8214,7 @@
         <v>0.73</v>
       </c>
       <c r="G305" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H305" s="4">
         <v>3</v>
@@ -8228,10 +8228,10 @@
         <v>46146</v>
       </c>
       <c r="C306" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D306" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E306" s="4">
         <v>2.5000000000000001E-3</v>
@@ -8240,7 +8240,7 @@
         <v>0.46</v>
       </c>
       <c r="G306" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H306" s="4">
         <v>3</v>
@@ -8254,10 +8254,10 @@
         <v>46146</v>
       </c>
       <c r="C307" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D307" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E307" s="4">
         <v>2.5000000000000001E-3</v>
@@ -8266,7 +8266,7 @@
         <v>0.37</v>
       </c>
       <c r="G307" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H307" s="4">
         <v>3</v>
@@ -8280,10 +8280,10 @@
         <v>46146</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D308" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E308" s="4">
         <v>2.5000000000000001E-3</v>
@@ -8292,7 +8292,7 @@
         <v>0.65</v>
       </c>
       <c r="G308" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H308" s="4">
         <v>4</v>
@@ -8306,10 +8306,10 @@
         <v>46146</v>
       </c>
       <c r="C309" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D309" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="E309" s="4">
         <v>2.5000000000000001E-3</v>
@@ -8318,7 +8318,7 @@
         <v>0.3</v>
       </c>
       <c r="G309" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H309" s="4">
         <v>4</v>
@@ -8332,10 +8332,10 @@
         <v>46146</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D310" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E310" s="4">
         <v>2.5000000000000001E-3</v>
@@ -8344,7 +8344,7 @@
         <v>0.53</v>
       </c>
       <c r="G310" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H310" s="4">
         <v>4</v>
@@ -8358,10 +8358,10 @@
         <v>46146</v>
       </c>
       <c r="C311" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D311" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E311" s="4">
         <v>2.5000000000000001E-3</v>
@@ -8370,7 +8370,7 @@
         <v>0.53</v>
       </c>
       <c r="G311" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H311" s="4">
         <v>4</v>
@@ -8384,10 +8384,10 @@
         <v>46146</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D312" s="4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E312" s="4">
         <v>2.5000000000000001E-3</v>
@@ -8396,7 +8396,7 @@
         <v>0.3</v>
       </c>
       <c r="G312" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H312" s="4">
         <v>4</v>
